--- a/TM_sem_outliers.xlsx
+++ b/TM_sem_outliers.xlsx
@@ -431,28 +431,34 @@
         </is>
       </c>
       <c r="C2">
-        <v>450</v>
+        <v>652</v>
       </c>
       <c r="D2">
-        <v>360</v>
+        <v>640</v>
       </c>
       <c r="E2">
-        <v>390</v>
+        <v>886.6666666666666</v>
       </c>
       <c r="F2">
-        <v>325</v>
-      </c>
-      <c r="G2">
-        <v>360</v>
+        <v>882.5</v>
       </c>
       <c r="H2">
-        <v>330</v>
+        <v>954</v>
+      </c>
+      <c r="I2">
+        <v>954</v>
       </c>
       <c r="J2">
-        <v>372.5</v>
+        <v>990</v>
+      </c>
+      <c r="K2">
+        <v>932</v>
       </c>
       <c r="L2">
-        <v>360</v>
+        <v>895</v>
+      </c>
+      <c r="M2">
+        <v>940</v>
       </c>
     </row>
     <row r="3">
@@ -508,34 +514,37 @@
         </is>
       </c>
       <c r="C4">
-        <v>486</v>
+        <v>697.5</v>
       </c>
       <c r="D4">
-        <v>893.3333333333334</v>
+        <v>812</v>
       </c>
       <c r="E4">
-        <v>736.6666666666666</v>
+        <v>820</v>
       </c>
       <c r="F4">
-        <v>553.3333333333334</v>
+        <v>834</v>
       </c>
       <c r="G4">
-        <v>547.5</v>
+        <v>826.6666666666666</v>
       </c>
       <c r="H4">
-        <v>370</v>
+        <v>806.6666666666666</v>
       </c>
       <c r="I4">
-        <v>766.6666666666666</v>
+        <v>820</v>
       </c>
       <c r="J4">
-        <v>1090</v>
+        <v>946.6666666666666</v>
       </c>
       <c r="K4">
-        <v>410</v>
+        <v>866.6666666666666</v>
       </c>
       <c r="L4">
-        <v>922.5</v>
+        <v>768.3333333333334</v>
+      </c>
+      <c r="M4">
+        <v>838.3333333333334</v>
       </c>
     </row>
     <row r="5">
@@ -548,34 +557,37 @@
         </is>
       </c>
       <c r="C5">
-        <v>346.6666666666667</v>
+        <v>905</v>
       </c>
       <c r="D5">
-        <v>790</v>
+        <v>960</v>
       </c>
       <c r="E5">
-        <v>1066</v>
+        <v>985</v>
       </c>
       <c r="F5">
-        <v>1032.5</v>
+        <v>972</v>
       </c>
       <c r="G5">
+        <v>915</v>
+      </c>
+      <c r="H5">
+        <v>962</v>
+      </c>
+      <c r="I5">
         <v>910</v>
       </c>
-      <c r="H5">
-        <v>1110</v>
-      </c>
-      <c r="I5">
-        <v>755</v>
-      </c>
       <c r="J5">
-        <v>1060</v>
+        <v>920</v>
+      </c>
+      <c r="K5">
+        <v>950</v>
       </c>
       <c r="L5">
-        <v>320</v>
+        <v>1003.333333333333</v>
       </c>
       <c r="M5">
-        <v>640</v>
+        <v>893.3333333333334</v>
       </c>
     </row>
     <row r="6">
@@ -674,34 +686,37 @@
         </is>
       </c>
       <c r="C8">
-        <v>488</v>
+        <v>420</v>
+      </c>
+      <c r="D8">
+        <v>385</v>
       </c>
       <c r="E8">
-        <v>410</v>
+        <v>460</v>
       </c>
       <c r="F8">
-        <v>430</v>
+        <v>323.3333333333333</v>
       </c>
       <c r="G8">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="H8">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="I8">
+        <v>385</v>
+      </c>
+      <c r="J8">
+        <v>362</v>
+      </c>
+      <c r="K8">
+        <v>488.3333333333333</v>
+      </c>
+      <c r="L8">
         <v>438</v>
       </c>
-      <c r="J8">
-        <v>315</v>
-      </c>
-      <c r="K8">
-        <v>830</v>
-      </c>
-      <c r="L8">
-        <v>386.6666666666667</v>
-      </c>
       <c r="M8">
-        <v>352.5</v>
+        <v>682</v>
       </c>
     </row>
     <row r="9">
@@ -714,34 +729,37 @@
         </is>
       </c>
       <c r="C9">
-        <v>705</v>
+        <v>430</v>
       </c>
       <c r="D9">
-        <v>455</v>
+        <v>417.5</v>
+      </c>
+      <c r="E9">
+        <v>486.6666666666667</v>
       </c>
       <c r="F9">
-        <v>380</v>
+        <v>505</v>
       </c>
       <c r="G9">
-        <v>452.5</v>
+        <v>490</v>
       </c>
       <c r="H9">
-        <v>445</v>
+        <v>426.6666666666667</v>
       </c>
       <c r="I9">
-        <v>480</v>
+        <v>533.3333333333334</v>
       </c>
       <c r="J9">
-        <v>375</v>
+        <v>521.6666666666666</v>
       </c>
       <c r="K9">
-        <v>415</v>
+        <v>538.3333333333334</v>
       </c>
       <c r="L9">
-        <v>424</v>
+        <v>530</v>
       </c>
       <c r="M9">
-        <v>642.5</v>
+        <v>612</v>
       </c>
     </row>
     <row r="10">
@@ -883,31 +901,37 @@
         </is>
       </c>
       <c r="C13">
-        <v>450</v>
+        <v>632</v>
+      </c>
+      <c r="D13">
+        <v>882.5</v>
       </c>
       <c r="E13">
-        <v>345</v>
+        <v>848</v>
+      </c>
+      <c r="F13">
+        <v>755</v>
       </c>
       <c r="G13">
-        <v>330</v>
+        <v>966</v>
       </c>
       <c r="H13">
-        <v>320</v>
+        <v>888.3333333333334</v>
       </c>
       <c r="I13">
-        <v>470</v>
+        <v>1018</v>
       </c>
       <c r="J13">
-        <v>575</v>
+        <v>928.3333333333334</v>
       </c>
       <c r="K13">
-        <v>550</v>
+        <v>974</v>
       </c>
       <c r="L13">
-        <v>780</v>
+        <v>1086</v>
       </c>
       <c r="M13">
-        <v>490</v>
+        <v>1038.333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -963,37 +987,37 @@
         </is>
       </c>
       <c r="C15">
-        <v>976</v>
+        <v>415</v>
       </c>
       <c r="D15">
-        <v>758.3333333333334</v>
+        <v>416</v>
       </c>
       <c r="E15">
-        <v>976.6666666666666</v>
+        <v>402</v>
       </c>
       <c r="F15">
-        <v>795</v>
+        <v>470</v>
       </c>
       <c r="G15">
-        <v>788</v>
+        <v>436</v>
       </c>
       <c r="H15">
-        <v>710</v>
+        <v>673.3333333333334</v>
       </c>
       <c r="I15">
-        <v>714</v>
+        <v>515</v>
       </c>
       <c r="J15">
-        <v>598</v>
+        <v>578.3333333333334</v>
       </c>
       <c r="K15">
-        <v>726.6666666666666</v>
+        <v>512</v>
       </c>
       <c r="L15">
-        <v>685</v>
+        <v>415</v>
       </c>
       <c r="M15">
-        <v>630</v>
+        <v>440</v>
       </c>
     </row>
     <row r="16">
@@ -1048,6 +1072,39 @@
           <t>GAG</t>
         </is>
       </c>
+      <c r="C17">
+        <v>460</v>
+      </c>
+      <c r="D17">
+        <v>384</v>
+      </c>
+      <c r="E17">
+        <v>476</v>
+      </c>
+      <c r="F17">
+        <v>556.6666666666666</v>
+      </c>
+      <c r="G17">
+        <v>696.6666666666666</v>
+      </c>
+      <c r="H17">
+        <v>552</v>
+      </c>
+      <c r="I17">
+        <v>596.6666666666666</v>
+      </c>
+      <c r="J17">
+        <v>622.5</v>
+      </c>
+      <c r="K17">
+        <v>528.3333333333334</v>
+      </c>
+      <c r="L17">
+        <v>555</v>
+      </c>
+      <c r="M17">
+        <v>546</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1116,6 +1173,9 @@
       <c r="H19">
         <v>796</v>
       </c>
+      <c r="I19">
+        <v>1066</v>
+      </c>
       <c r="J19">
         <v>1030</v>
       </c>
@@ -1138,6 +1198,9 @@
           <t>GAG</t>
         </is>
       </c>
+      <c r="C20">
+        <v>1130</v>
+      </c>
       <c r="D20">
         <v>1010</v>
       </c>
@@ -1740,11 +1803,17 @@
       <c r="D34">
         <v>755</v>
       </c>
+      <c r="E34">
+        <v>980</v>
+      </c>
       <c r="F34">
         <v>1115</v>
       </c>
       <c r="G34">
         <v>1086.666666666667</v>
+      </c>
+      <c r="J34">
+        <v>1011.666666666667</v>
       </c>
       <c r="K34">
         <v>510</v>
@@ -1981,37 +2050,37 @@
         </is>
       </c>
       <c r="C40">
-        <v>512.5</v>
+        <v>590</v>
       </c>
       <c r="D40">
-        <v>446</v>
+        <v>641.6666666666666</v>
       </c>
       <c r="E40">
-        <v>430</v>
+        <v>813.3333333333334</v>
       </c>
       <c r="F40">
-        <v>355</v>
+        <v>694</v>
       </c>
       <c r="G40">
-        <v>720</v>
+        <v>868.3333333333334</v>
       </c>
       <c r="H40">
-        <v>424</v>
+        <v>931.6666666666666</v>
       </c>
       <c r="I40">
-        <v>463.3333333333333</v>
+        <v>946.6666666666666</v>
       </c>
       <c r="J40">
-        <v>383.3333333333333</v>
+        <v>943.3333333333334</v>
       </c>
       <c r="K40">
-        <v>350</v>
+        <v>730</v>
       </c>
       <c r="L40">
-        <v>645</v>
+        <v>868.3333333333334</v>
       </c>
       <c r="M40">
-        <v>410</v>
+        <v>751.6666666666666</v>
       </c>
     </row>
     <row r="41">
